--- a/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/差旅报销单-支持打印A4.xlsx
+++ b/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/差旅报销单-支持打印A4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aLJD\server\oa\dh-oa\dh-module-oa\dh-module-oa-server\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8A1D7D-09C5-406A-894A-336AD0B4BF22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354A2583-78F2-4F76-AB14-058AFEA1ECCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="3015" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="差旅报销单" sheetId="1" r:id="rId1"/>
@@ -424,15 +424,31 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -440,16 +456,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -458,25 +471,12 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -778,71 +778,71 @@
   <sheetData>
     <row r="1" spans="1:11" ht="45" customHeight="1"/>
     <row r="2" spans="1:11" ht="20.25" customHeight="1">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="13"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="21"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="26"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="31"/>
       <c r="C3" s="9"/>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="17" t="s">
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="18"/>
+      <c r="K3" s="24"/>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="22" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
       <c r="G4" s="15"/>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
       <c r="K4" s="15"/>
     </row>
     <row r="5" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
       <c r="F5" s="15"/>
-      <c r="G5" s="29" t="s">
+      <c r="G5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="22"/>
+      <c r="H5" s="13"/>
       <c r="I5" s="15"/>
-      <c r="J5" s="29" t="s">
+      <c r="J5" s="14" t="s">
         <v>8</v>
       </c>
       <c r="K5" s="15"/>
@@ -905,13 +905,13 @@
         <v>23</v>
       </c>
       <c r="H7" s="2"/>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="11" t="s">
         <v>24</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="K7" s="35" t="s">
+      <c r="K7" s="11" t="s">
         <v>26</v>
       </c>
     </row>
@@ -926,7 +926,7 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
-      <c r="K8" s="35"/>
+      <c r="K8" s="11"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
       <c r="A9" s="6"/>
@@ -939,7 +939,7 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="35"/>
+      <c r="K9" s="11"/>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1">
       <c r="A10" s="6"/>
@@ -952,7 +952,7 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
-      <c r="K10" s="35"/>
+      <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1">
       <c r="A11" s="6"/>
@@ -965,7 +965,7 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="35"/>
+      <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1">
       <c r="A12" s="6"/>
@@ -978,7 +978,7 @@
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
-      <c r="K12" s="35"/>
+      <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1">
       <c r="A13" s="6"/>
@@ -991,7 +991,7 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
-      <c r="K13" s="35"/>
+      <c r="K13" s="11"/>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1">
       <c r="A14" s="6"/>
@@ -1004,17 +1004,17 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
-      <c r="K14" s="35"/>
+      <c r="K14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="33" t="s">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G15" s="15"/>
@@ -1032,15 +1032,15 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="21.75" customHeight="1">
-      <c r="A16" s="30"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="27" t="s">
+      <c r="A16" s="33"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G16" s="22"/>
+      <c r="G16" s="13"/>
       <c r="H16" s="2">
         <v>1</v>
       </c>
@@ -1050,20 +1050,20 @@
       <c r="J16" s="2">
         <v>80</v>
       </c>
-      <c r="K16" s="35" t="s">
+      <c r="K16" s="11" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="20.65" customHeight="1">
-      <c r="A17" s="31"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="27" t="s">
+      <c r="A17" s="34"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="22"/>
+      <c r="G17" s="13"/>
       <c r="H17" s="10">
         <v>1</v>
       </c>
@@ -1073,79 +1073,70 @@
       <c r="J17" s="2">
         <v>100</v>
       </c>
-      <c r="K17" s="35" t="s">
+      <c r="K17" s="11" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="27.4" customHeight="1">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="22"/>
+      <c r="B18" s="13"/>
       <c r="C18" s="15"/>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
       <c r="G18" s="15"/>
-      <c r="H18" s="14" t="s">
+      <c r="H18" s="16" t="s">
         <v>38</v>
       </c>
       <c r="I18" s="15"/>
-      <c r="J18" s="20" t="s">
+      <c r="J18" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="K18" s="34"/>
+      <c r="K18" s="26"/>
     </row>
     <row r="19" spans="1:11" ht="27.4" customHeight="1">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="22"/>
+      <c r="B19" s="13"/>
       <c r="C19" s="15"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
       <c r="G19" s="15"/>
-      <c r="H19" s="14" t="s">
+      <c r="H19" s="16" t="s">
         <v>41</v>
       </c>
       <c r="I19" s="15"/>
-      <c r="J19" s="14"/>
+      <c r="J19" s="16"/>
       <c r="K19" s="15"/>
     </row>
     <row r="20" spans="1:11" ht="32.1" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="12"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="18"/>
       <c r="D20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="19"/>
-      <c r="F20" s="12"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="18"/>
       <c r="G20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H20" s="19"/>
-      <c r="I20" s="12"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="18"/>
       <c r="J20" s="1" t="s">
         <v>45</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="D19:G19"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="A4:B4"/>
@@ -1162,6 +1153,15 @@
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="H20:I20"/>
     <mergeCell ref="A15:E17"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="D19:G19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>

--- a/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/差旅报销单-支持打印A4.xlsx
+++ b/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/差旅报销单-支持打印A4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aLJD\server\oa\dh-oa\dh-module-oa\dh-module-oa-server\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354A2583-78F2-4F76-AB14-058AFEA1ECCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C778FE96-C47E-4DFA-82D2-A525352A62FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-225" yWindow="1140" windowWidth="28830" windowHeight="14820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="差旅报销单" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="45">
   <si>
     <t>差 旅 费 报 销 单</t>
   </si>
@@ -89,9 +89,6 @@
   </si>
   <si>
     <t>{.destination}</t>
-  </si>
-  <si>
-    <t>{.transportType}</t>
   </si>
   <si>
     <t>{.trafficAmount}</t>
@@ -406,10 +403,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -436,6 +429,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
@@ -795,7 +794,7 @@
     <row r="3" spans="1:11" ht="15" customHeight="1">
       <c r="A3" s="30"/>
       <c r="B3" s="31"/>
-      <c r="C3" s="9"/>
+      <c r="C3" s="7"/>
       <c r="D3" s="28" t="s">
         <v>1</v>
       </c>
@@ -813,77 +812,77 @@
       <c r="A4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="13"/>
+      <c r="C4" s="6" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="27"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="15"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="13"/>
       <c r="H4" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="15"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="13"/>
     </row>
     <row r="5" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="14" t="s">
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="14" t="s">
+      <c r="H5" s="11"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="15"/>
+      <c r="K5" s="13"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -901,22 +900,20 @@
       <c r="F7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="11" t="s">
+      <c r="J7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="K7" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="K7" s="11" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1">
-      <c r="A8" s="6"/>
+      <c r="A8" s="4"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -926,10 +923,10 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
-      <c r="K8" s="11"/>
+      <c r="K8" s="9"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
-      <c r="A9" s="6"/>
+      <c r="A9" s="4"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -939,10 +936,10 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="11"/>
+      <c r="K9" s="9"/>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1">
-      <c r="A10" s="6"/>
+      <c r="A10" s="4"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -952,10 +949,10 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
-      <c r="K10" s="11"/>
+      <c r="K10" s="9"/>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1">
-      <c r="A11" s="6"/>
+      <c r="A11" s="4"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -965,10 +962,10 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="11"/>
+      <c r="K11" s="9"/>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1">
-      <c r="A12" s="6"/>
+      <c r="A12" s="4"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -978,10 +975,10 @@
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
-      <c r="K12" s="11"/>
+      <c r="K12" s="9"/>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1">
-      <c r="A13" s="6"/>
+      <c r="A13" s="4"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -991,10 +988,10 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
-      <c r="K13" s="11"/>
+      <c r="K13" s="9"/>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1">
-      <c r="A14" s="6"/>
+      <c r="A14" s="4"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -1004,11 +1001,11 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
-      <c r="K14" s="11"/>
+      <c r="K14" s="9"/>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1">
-      <c r="A15" s="14" t="s">
-        <v>27</v>
+      <c r="A15" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
@@ -1017,17 +1014,17 @@
       <c r="F15" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="15"/>
-      <c r="H15" s="5" t="s">
+      <c r="G15" s="13"/>
+      <c r="H15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="J15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J15" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K15" s="5" t="s">
+      <c r="K15" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1037,21 +1034,21 @@
       <c r="C16" s="31"/>
       <c r="D16" s="31"/>
       <c r="E16" s="24"/>
-      <c r="F16" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="13"/>
+      <c r="F16" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="11"/>
       <c r="H16" s="2">
         <v>1</v>
       </c>
-      <c r="I16" s="4" t="s">
-        <v>32</v>
+      <c r="I16" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="J16" s="2">
         <v>80</v>
       </c>
-      <c r="K16" s="11" t="s">
-        <v>33</v>
+      <c r="K16" s="9" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="20.65" customHeight="1">
@@ -1060,79 +1057,79 @@
       <c r="C17" s="29"/>
       <c r="D17" s="29"/>
       <c r="E17" s="35"/>
-      <c r="F17" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" s="13"/>
-      <c r="H17" s="10">
+      <c r="F17" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="11"/>
+      <c r="H17" s="8">
         <v>1</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>32</v>
+      <c r="I17" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="J17" s="2">
         <v>100</v>
       </c>
-      <c r="K17" s="11" t="s">
+      <c r="K17" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="27.4" customHeight="1">
+      <c r="A18" s="14" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" ht="27.4" customHeight="1">
-      <c r="A18" s="16" t="s">
+      <c r="B18" s="11"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="16" t="s">
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="16" t="s">
+      <c r="I18" s="13"/>
+      <c r="J18" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="I18" s="15"/>
-      <c r="J18" s="25" t="s">
+      <c r="K18" s="26"/>
+    </row>
+    <row r="19" spans="1:11" ht="27.4" customHeight="1">
+      <c r="A19" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="K18" s="26"/>
-    </row>
-    <row r="19" spans="1:11" ht="27.4" customHeight="1">
-      <c r="A19" s="16" t="s">
+      <c r="B19" s="11"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="I19" s="15"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="15"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="16"/>
     </row>
     <row r="20" spans="1:11" ht="32.1" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
       <c r="D20" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="18"/>
       <c r="J20" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/差旅报销单-支持打印A4.xlsx
+++ b/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/差旅报销单-支持打印A4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aLJD\server\oa\dh-oa\dh-module-oa\dh-module-oa-server\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C778FE96-C47E-4DFA-82D2-A525352A62FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229B64CC-56C3-4294-9D7A-5E34ECCA1622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-225" yWindow="1140" windowWidth="28830" windowHeight="14820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="3015" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="差旅报销单" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="48">
   <si>
     <t>差 旅 费 报 销 单</t>
   </si>
@@ -155,6 +155,18 @@
   </si>
   <si>
     <t>经手</t>
+  </si>
+  <si>
+    <t>{.transportType}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.receiptCount}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{receiptCount}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -409,9 +421,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -420,34 +429,18 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -455,6 +448,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -462,6 +458,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -470,12 +467,27 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -777,74 +789,74 @@
   <sheetData>
     <row r="1" spans="1:11" ht="45" customHeight="1"/>
     <row r="2" spans="1:11" ht="20.25" customHeight="1">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="21"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="12"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1">
-      <c r="A3" s="30"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="28" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="23" t="s">
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="24"/>
+      <c r="K3" s="17"/>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="14"/>
+      <c r="C4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="32" t="s">
+      <c r="D4" s="21"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="13"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="14"/>
     </row>
     <row r="5" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="12" t="s">
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="11"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="12" t="s">
+      <c r="H5" s="22"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="13"/>
+      <c r="K5" s="14"/>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="3" t="s">
@@ -900,15 +912,19 @@
       <c r="F7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="9" t="s">
+      <c r="G7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="K7" s="8" t="s">
         <v>25</v>
       </c>
     </row>
@@ -923,7 +939,7 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
-      <c r="K8" s="9"/>
+      <c r="K8" s="8"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
       <c r="A9" s="4"/>
@@ -936,7 +952,7 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="9"/>
+      <c r="K9" s="8"/>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1">
       <c r="A10" s="4"/>
@@ -949,7 +965,7 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
-      <c r="K10" s="9"/>
+      <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1">
       <c r="A11" s="4"/>
@@ -962,7 +978,7 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="9"/>
+      <c r="K11" s="8"/>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1">
       <c r="A12" s="4"/>
@@ -975,7 +991,7 @@
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
-      <c r="K12" s="9"/>
+      <c r="K12" s="8"/>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1">
       <c r="A13" s="4"/>
@@ -988,7 +1004,7 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
-      <c r="K13" s="9"/>
+      <c r="K13" s="8"/>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1">
       <c r="A14" s="4"/>
@@ -1001,20 +1017,20 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
-      <c r="K14" s="9"/>
+      <c r="K14" s="8"/>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="19" t="s">
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="13"/>
+      <c r="G15" s="14"/>
       <c r="H15" s="3" t="s">
         <v>27</v>
       </c>
@@ -1029,15 +1045,15 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="21.75" customHeight="1">
-      <c r="A16" s="33"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="10" t="s">
+      <c r="A16" s="30"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="11"/>
+      <c r="G16" s="22"/>
       <c r="H16" s="2">
         <v>1</v>
       </c>
@@ -1047,21 +1063,21 @@
       <c r="J16" s="2">
         <v>80</v>
       </c>
-      <c r="K16" s="9" t="s">
+      <c r="K16" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="20.65" customHeight="1">
-      <c r="A17" s="34"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="10" t="s">
+      <c r="A17" s="31"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="8">
+      <c r="G17" s="22"/>
+      <c r="H17" s="7">
         <v>1</v>
       </c>
       <c r="I17" s="2" t="s">
@@ -1070,70 +1086,81 @@
       <c r="J17" s="2">
         <v>100</v>
       </c>
-      <c r="K17" s="9" t="s">
+      <c r="K17" s="8" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="27.4" customHeight="1">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="14" t="s">
+      <c r="B18" s="22"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="14" t="s">
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="13"/>
-      <c r="J18" s="25" t="s">
+      <c r="I18" s="14"/>
+      <c r="J18" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="K18" s="26"/>
-    </row>
-    <row r="19" spans="1:11" ht="27.4" customHeight="1">
-      <c r="A19" s="14" t="s">
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="1:11" ht="37.5" customHeight="1">
+      <c r="A19" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="14" t="s">
+      <c r="B19" s="22"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I19" s="13"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="16"/>
-    </row>
-    <row r="20" spans="1:11" ht="32.1" customHeight="1">
+      <c r="I19" s="14"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="34"/>
+    </row>
+    <row r="20" spans="1:11" ht="42.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="11"/>
       <c r="D20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="17"/>
-      <c r="F20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="11"/>
       <c r="G20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="17"/>
-      <c r="I20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="11"/>
       <c r="J20" s="1" t="s">
         <v>44</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="D19:G19"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="A4:B4"/>
@@ -1150,15 +1177,6 @@
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="H20:I20"/>
     <mergeCell ref="A15:E17"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="D19:G19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>

--- a/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/差旅报销单-支持打印A4.xlsx
+++ b/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/差旅报销单-支持打印A4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aLJD\server\oa\dh-oa\dh-module-oa\dh-module-oa-server\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229B64CC-56C3-4294-9D7A-5E34ECCA1622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23930C08-A638-4AED-B397-71EEE1DD9DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="3015" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
   <si>
     <t>差 旅 费 报 销 单</t>
   </si>
@@ -166,6 +166,10 @@
   </si>
   <si>
     <t>{receiptCount}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{subsidyPeople}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -432,15 +436,34 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -448,9 +471,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -458,7 +478,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -467,27 +486,12 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -789,74 +793,74 @@
   <sheetData>
     <row r="1" spans="1:11" ht="45" customHeight="1"/>
     <row r="2" spans="1:11" ht="20.25" customHeight="1">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="12"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="21"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="26"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="31"/>
       <c r="C3" s="6"/>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="16" t="s">
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="17"/>
+      <c r="K3" s="24"/>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="14"/>
+      <c r="B4" s="13"/>
       <c r="C4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="28" t="s">
+      <c r="D4" s="27"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="14"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="13"/>
     </row>
     <row r="5" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="29" t="s">
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="22"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="29" t="s">
+      <c r="H5" s="11"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="14"/>
+      <c r="K5" s="13"/>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="3" t="s">
@@ -1020,17 +1024,17 @@
       <c r="K14" s="8"/>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="35" t="s">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="14"/>
+      <c r="G15" s="13"/>
       <c r="H15" s="3" t="s">
         <v>27</v>
       </c>
@@ -1045,17 +1049,17 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="21.75" customHeight="1">
-      <c r="A16" s="30"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="27" t="s">
+      <c r="A16" s="33"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="22"/>
-      <c r="H16" s="2">
-        <v>1</v>
+      <c r="G16" s="11"/>
+      <c r="H16" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>31</v>
@@ -1068,17 +1072,17 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="20.65" customHeight="1">
-      <c r="A17" s="31"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="27" t="s">
+      <c r="A17" s="34"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G17" s="22"/>
-      <c r="H17" s="7">
-        <v>1</v>
+      <c r="G17" s="11"/>
+      <c r="H17" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>31</v>
@@ -1091,76 +1095,67 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="27.4" customHeight="1">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="13" t="s">
+      <c r="B18" s="11"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="13" t="s">
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="14"/>
-      <c r="J18" s="19" t="s">
+      <c r="I18" s="13"/>
+      <c r="J18" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="K18" s="20"/>
+      <c r="K18" s="26"/>
     </row>
     <row r="19" spans="1:11" ht="37.5" customHeight="1">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="13" t="s">
+      <c r="B19" s="11"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="13" t="s">
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="I19" s="14"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="34"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="16"/>
     </row>
     <row r="20" spans="1:11" ht="42.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="18"/>
-      <c r="C20" s="11"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="18"/>
       <c r="D20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="18"/>
-      <c r="F20" s="11"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="18"/>
       <c r="G20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="18"/>
-      <c r="I20" s="11"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="18"/>
       <c r="J20" s="1" t="s">
         <v>44</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="D19:G19"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="A4:B4"/>
@@ -1177,6 +1172,15 @@
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="H20:I20"/>
     <mergeCell ref="A15:E17"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="D19:G19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>

--- a/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/差旅报销单-支持打印A4.xlsx
+++ b/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/差旅报销单-支持打印A4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aLJD\server\oa\dh-oa\dh-module-oa\dh-module-oa-server\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23930C08-A638-4AED-B397-71EEE1DD9DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E25AAC-D1D3-4ADB-81B9-6150AB172A29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="3015" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="51">
   <si>
     <t>差 旅 费 报 销 单</t>
   </si>
@@ -115,16 +115,7 @@
     <t>市内交通费</t>
   </si>
   <si>
-    <t>{subsidyDays}</t>
-  </si>
-  <si>
-    <t>{subsidyCityAmount}</t>
-  </si>
-  <si>
     <t>伙食补贴费</t>
-  </si>
-  <si>
-    <t>{subsidyMealAmount}</t>
   </si>
   <si>
     <t>合计大写</t>
@@ -169,7 +160,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{subsidyPeople}</t>
+    <t>{trafficSubsidyDays}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{trafficSubsidyPeople}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{trafficSubsidyAmount}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{mealSubsidyDays}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{mealSubsidyPeople}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{mealSubsidyAmount}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -411,7 +422,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
@@ -427,43 +438,21 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -471,6 +460,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -478,6 +470,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -486,12 +479,27 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -793,71 +801,71 @@
   <sheetData>
     <row r="1" spans="1:11" ht="45" customHeight="1"/>
     <row r="2" spans="1:11" ht="20.25" customHeight="1">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="21"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="11"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1">
-      <c r="A3" s="30"/>
-      <c r="B3" s="31"/>
+      <c r="A3" s="24"/>
+      <c r="B3" s="25"/>
       <c r="C3" s="6"/>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="23" t="s">
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="24"/>
+      <c r="K3" s="16"/>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="14" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="32" t="s">
+      <c r="H4" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
       <c r="K4" s="13"/>
     </row>
     <row r="5" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
       <c r="F5" s="13"/>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="11"/>
+      <c r="H5" s="21"/>
       <c r="I5" s="13"/>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="28" t="s">
         <v>8</v>
       </c>
       <c r="K5" s="13"/>
@@ -917,18 +925,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -943,7 +951,7 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
-      <c r="K8" s="8"/>
+      <c r="K8" s="7"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
       <c r="A9" s="4"/>
@@ -956,7 +964,7 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="8"/>
+      <c r="K9" s="7"/>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1">
       <c r="A10" s="4"/>
@@ -969,7 +977,7 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
-      <c r="K10" s="8"/>
+      <c r="K10" s="7"/>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1">
       <c r="A11" s="4"/>
@@ -982,7 +990,7 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="8"/>
+      <c r="K11" s="7"/>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1">
       <c r="A12" s="4"/>
@@ -995,7 +1003,7 @@
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
-      <c r="K12" s="8"/>
+      <c r="K12" s="7"/>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1">
       <c r="A13" s="4"/>
@@ -1008,7 +1016,7 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
-      <c r="K13" s="8"/>
+      <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1">
       <c r="A14" s="4"/>
@@ -1021,17 +1029,17 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
-      <c r="K14" s="8"/>
+      <c r="K14" s="7"/>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="19" t="s">
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="34" t="s">
         <v>16</v>
       </c>
       <c r="G15" s="13"/>
@@ -1049,113 +1057,122 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="21.75" customHeight="1">
-      <c r="A16" s="33"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="10" t="s">
+      <c r="A16" s="29"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="11"/>
+      <c r="G16" s="21"/>
       <c r="H16" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="J16" s="2">
         <v>80</v>
       </c>
-      <c r="K16" s="8" t="s">
-        <v>32</v>
+      <c r="K16" s="7" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="20.65" customHeight="1">
-      <c r="A17" s="34"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="7" t="s">
+      <c r="A17" s="30"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" s="21"/>
+      <c r="H17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="J17" s="2">
         <v>100</v>
       </c>
-      <c r="K17" s="8" t="s">
+      <c r="K17" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="27.4" customHeight="1">
+      <c r="A18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="12" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" ht="27.4" customHeight="1">
-      <c r="A18" s="14" t="s">
+      <c r="I18" s="13"/>
+      <c r="J18" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="14" t="s">
+      <c r="K18" s="19"/>
+    </row>
+    <row r="19" spans="1:11" ht="37.5" customHeight="1">
+      <c r="A19" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="14" t="s">
+      <c r="B19" s="21"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="13"/>
-      <c r="J18" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="K18" s="26"/>
-    </row>
-    <row r="19" spans="1:11" ht="37.5" customHeight="1">
-      <c r="A19" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="14" t="s">
-        <v>40</v>
-      </c>
       <c r="I19" s="13"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="16"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="33"/>
     </row>
     <row r="20" spans="1:11" ht="42.75" customHeight="1">
       <c r="A20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="17"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="17"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H20" s="17"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E20" s="17"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20" s="17"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="D19:G19"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="A4:B4"/>
@@ -1172,15 +1189,6 @@
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="H20:I20"/>
     <mergeCell ref="A15:E17"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="D19:G19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
